--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/26,10,26 Останкино КИ и ЗПФ/дв 26,10,26 мррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/26,10,26 Останкино КИ и ЗПФ/дв 26,10,26 мррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\26,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E655B5-D7DF-4966-958C-0356009119A5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376896B3-2CEA-4586-9F97-F73FB8510B88}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$Z$107</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
